--- a/benchmark/generated_files/CC-1_V_027.xlsx
+++ b/benchmark/generated_files/CC-1_V_027.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A2:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -442,73 +442,73 @@
     <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Intestatario: Marco Rossi + Laura Bianchi</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tipo conto: Conto corrente</t>
+          <t>Movimenti al 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Filiale: SEDE CENTRALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Intestatario: Marco Rossi + Laura Bianchi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saldo iniziale: 14.399,89 EUR</t>
+          <t>Codice cliente: 818123</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Saldo iniziale: 3.998,44 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tipo conto: Conto corrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>IBAN: IT60 X054 2811 1010 0000 0123 456</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Periodo: 01/01/2026 - 28/02/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Banca: Intesa Sanpaolo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Codice cliente: 669619</t>
+          <t>Periodo: 01/01/2026 - 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Banca: Intesa Sanpaolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
@@ -540,11 +540,11 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 94,70 EUR DEL 01.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>GIROCONTO DA CC 0123456 A CC 0468012 ACCANTONAMENTO RISPARMIO</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-94.7</v>
+        <v>-451.57</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -554,15 +554,15 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210585896</t>
+          <t>Pagam. POS - PAGAMENTO POS 683,90 EUR DEL 04.01.2026 A (ITA) FUNSIDE NAPOLI</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-5.4</v>
+        <v>-683.9</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -572,15 +572,15 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 713,16 EUR DEL 02.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
+          <t>Bonif. v/fav. - RIF:210884213 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-713.16</v>
+        <v>236.89</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -590,15 +590,15 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6493 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-340.83</v>
+        <v>-25.17</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -608,15 +608,15 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:213374365 BEN. CONDOMINIO RESIDENZA MARE</t>
+          <t>Pagam. POS - PAGAMENTO POS 6,03 EUR DEL 09.01.2026 A (ITA) NATURA BRESCIA</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-110.93</v>
+        <v>-6.03</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -626,15 +626,15 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218539788 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Pagam. POS - PAGAMENTO POS 145,55 EUR DEL 11.01.2026 A (ITA) MERCATÒ BIG BERGAMO</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>210.44</v>
+        <v>-145.55</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -644,15 +644,15 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46027</v>
+        <v>46033</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214218201 BEN. VERDI ROSA AIUTO NIPOTE</t>
+          <t>Bonif. v/fav. - RIF:214796901 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-387.41</v>
+        <v>64.59</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -662,15 +662,15 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0123456 A CC 0075849</t>
+          <t>Disposizione - RIF:214271754 BEN. CONDOMINIO VIA ROMA 15</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-730</v>
+        <v>-126.46</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -680,15 +680,15 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:211820677 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3991 OAKBERRY AÇAÍ BOWLS</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-71.8</v>
+        <v>-63.28</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -698,15 +698,15 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:218856244 BEN. RICARICA POSTEPAY SOFIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,58 EUR DEL 15.01.2026 A (ITA) TABACCHERIA N.12</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-139.14</v>
+        <v>-35.58</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -716,15 +716,15 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 4084 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 93,34 EUR DEL 16.01.2026 A (ITA) NATURA</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-105.06</v>
+        <v>-93.34</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -734,15 +734,15 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46036</v>
+        <v>46042</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 105,04 EUR DEL 14.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2973 FLOWER BURGER</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-105.04</v>
+        <v>-48.44</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -752,15 +752,15 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46039</v>
+        <v>46042</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-193.1</v>
+        <v>-12.65</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -770,15 +770,15 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214341333 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7820 NAU! PARMA</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>309.28</v>
+        <v>-182.93</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -788,15 +788,15 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:216792445 BEN. RICARICA REVOLUT LAURA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2549 DR. MAX TORINO</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-199.72</v>
+        <v>-39.28</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -806,15 +806,15 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7473 OVS S.P.A.</t>
+          <t>Disposizione - RIF:210673134 BEN. IDRAULICO ROSSI PAOLO</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-76.83</v>
+        <v>-45.89</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -824,15 +824,15 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,58 EUR DEL 23.01.2026 A (ITA) STARBUCKS RESERVE</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-10.64</v>
+        <v>-81.58</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -842,15 +842,15 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 86,00 EUR DEL 25.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>GIROCONTO DA CC 0123456 A CC 0468012 ACCANTONAMENTO RISPARMIO</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-86</v>
+        <v>-476.82</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -864,11 +864,11 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:218166533 BEN. CONTO ARANCIO ACCANTONAMENTO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8776 IKEA CAFÉ</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-534.84</v>
+        <v>-30.18</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -878,15 +878,15 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212702473 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 126,63 EUR DEL 26.01.2026 A (ITA) TIGRE AMICO</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2101.05</v>
+        <v>-126.63</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -900,11 +900,11 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218553014 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2068.04</v>
+        <v>2086.01</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -918,11 +918,11 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:213936074 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2055.91</v>
+        <v>2135.66</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2073.82</v>
+        <v>2149.76</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -954,11 +954,11 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216341872 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2076.63</v>
+        <v>2129.9</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -972,11 +972,11 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218694087 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2085.54</v>
+        <v>2113.89</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -990,11 +990,11 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211728484 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2120.72</v>
+        <v>2109.3</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1008,11 +1008,11 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:217869293 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2147.06</v>
+        <v>2089</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1026,11 +1026,11 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217186119 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:215993263 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2125.94</v>
+        <v>2135.46</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2135.41</v>
+        <v>2129.72</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218899743 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:212850405 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2081.68</v>
+        <v>2058.23</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1080,11 +1080,11 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217784414 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:210638330 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2130.41</v>
+        <v>2131.99</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -1098,11 +1098,11 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214210028 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:216960039 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2121.53</v>
+        <v>2144.13</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -1116,11 +1116,11 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217878309 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2118.45</v>
+        <v>2120.72</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2141.8</v>
+        <v>2122.3</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -1152,11 +1152,11 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215847154 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:211156752 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2136.7</v>
+        <v>2076.35</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213769135 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:213666023 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2139.05</v>
+        <v>2115.07</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217371274 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2107.66</v>
+        <v>2123.12</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2089.29</v>
+        <v>2070.8</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215134282 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:213943305 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2102.42</v>
+        <v>2107.42</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -1242,11 +1242,11 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218575042 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2094.22</v>
+        <v>2070.58</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -1256,15 +1256,15 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219132635 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:215965385 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>2091.64</v>
+        <v>383.93</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -1274,15 +1274,15 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213547699 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>2137.49</v>
+        <v>-241.86</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -1292,15 +1292,15 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:215422541 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2096.09</v>
+        <v>128.09</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -1310,15 +1310,15 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9359 JOHNSON FITNESS &amp; WELLNESS EUR</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>2149.05</v>
+        <v>-21.62</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -1328,15 +1328,15 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Pagam. POS - PAGAMENTO POS 40,73 EUR DEL 01.02.2026 A (ITA) JULIUS MEINL</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2067.07</v>
+        <v>-40.73</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -1346,15 +1346,15 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI GENNAIO 2026</t>
+          <t>Disposizione - RIF:215815820 BEN. RICARICA POSTEPAY SOFIA</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2077.86</v>
+        <v>-240.52</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -1364,15 +1364,15 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214021642 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Disposizione - RIF:218283087 BEN. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>2098.63</v>
+        <v>-132.56</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -1382,15 +1382,15 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214309910 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Addebito SDD - JUST EAT ITALY SRL</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>2098.18</v>
+        <v>-49.45</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -1400,15 +1400,15 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46051</v>
+        <v>46068</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 31,36 EUR DEL 29.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>Disposizione - RIF:216603239 BEN. VERDI ROSA AIUTO NIPOTE</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>-31.36</v>
+        <v>-519.5</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -1418,15 +1418,15 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46051</v>
+        <v>46069</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9245 CONAD SUPERSTORE</t>
+          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>-46.45</v>
+        <v>-30.42</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
@@ -1436,15 +1436,15 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46051</v>
+        <v>46069</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 BEN. SOFIA ROSSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 66,39 EUR DEL 16.02.2026 A (ITA) TIGRE</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>-104.78</v>
+        <v>-66.39</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -1454,15 +1454,15 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46053</v>
+        <v>46070</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ENI PLENITUDE GAS E LUCE</t>
+          <t>Bonif. v/fav. - RIF:218011321 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>-39.93</v>
+        <v>421.2</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -1472,15 +1472,15 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46056</v>
+        <v>46070</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9745 OVS S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:219712311 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>-145.69</v>
+        <v>494.94</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -1490,15 +1490,15 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46056</v>
+        <v>46073</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 20,52 EUR DEL 03.02.2026 A (ITA) FARMACIA DR ROSSI</t>
+          <t>Disposizione - RIF:215595038 BEN. IDRAULICO ROSSI PAOLO</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>-20.52</v>
+        <v>-175.83</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -1508,15 +1508,15 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46058</v>
+        <v>46075</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217216069 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Pagam. POS - PAGAMENTO POS 113,33 EUR DEL 22.02.2026 A (ITA) MERCATÒ</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>51.61</v>
+        <v>-113.33</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -1526,15 +1526,15 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46058</v>
+        <v>46077</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213770923 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Pagam. POS - PAGAMENTO POS 120,50 EUR DEL 24.02.2026 A (ITA) KÖRPERFORMEN</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>390.88</v>
+        <v>-120.5</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -1544,15 +1544,15 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46060</v>
+        <v>46078</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>-508.71</v>
+        <v>-294.57</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -1562,15 +1562,15 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46061</v>
+        <v>46080</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Bonif. v/fav. - RIF:215141927 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>-7.99</v>
+        <v>2076.63</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -1580,15 +1580,15 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46063</v>
+        <v>46080</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Bonif. v/fav. - RIF:219523235 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>-14.68</v>
+        <v>2083.95</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -1598,15 +1598,15 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46064</v>
+        <v>46080</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 637,47 EUR DEL 11.02.2026 A (ITA) LIBRERIA FELTRINELLI</t>
+          <t>Bonif. v/fav. - RIF:213986887 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>-637.47</v>
+        <v>2067.96</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -1616,15 +1616,15 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46065</v>
+        <v>46080</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211351890 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Bonif. v/fav. - RIF:214222411 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>139.64</v>
+        <v>2077.31</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -1634,15 +1634,15 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46068</v>
+        <v>46080</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211594125 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Bonif. v/fav. - RIF:210796008 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>150.16</v>
+        <v>2143.98</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -1652,15 +1652,15 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46070</v>
+        <v>46080</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 172,54 EUR DEL 17.02.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>-172.54</v>
+        <v>2061.42</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -1670,15 +1670,15 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46071</v>
+        <v>46080</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 165,03 EUR DEL 18.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Bonif. v/fav. - RIF:211717571 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>-165.03</v>
+        <v>2093.78</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -1688,15 +1688,15 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46074</v>
+        <v>46080</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212143790 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Bonif. v/fav. - RIF:216387534 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>-21.73</v>
+        <v>2053.67</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -1706,15 +1706,15 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
+          <t>Bonif. v/fav. - RIF:214138787 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>-115.83</v>
+        <v>2072.28</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -1728,11 +1728,11 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:215430257 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2061.72</v>
+        <v>2123.99</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -1746,11 +1746,11 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219947474 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2134.22</v>
+        <v>2122.98</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -1764,11 +1764,11 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214812530 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:218831475 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2057.46</v>
+        <v>2133.85</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2086.81</v>
+        <v>2148.27</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -1800,11 +1800,11 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:217503815 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2116.77</v>
+        <v>2126.38</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -1818,11 +1818,11 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
+          <t>Bonif. v/fav. - RIF:215540810 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2115.42</v>
+        <v>2106.01</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2088.59</v>
+        <v>2082.78</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -1854,11 +1854,11 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218625997 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2065.77</v>
+        <v>2054.83</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -1872,11 +1872,11 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219579172 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:213032219 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2128.29</v>
+        <v>2074.98</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -1890,11 +1890,11 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211746373 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>Bonif. v/fav. - RIF:217652763 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2065.23</v>
+        <v>2074.02</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -1908,11 +1908,11 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211008884 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2123.11</v>
+        <v>2051.74</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>2115.54</v>
+        <v>2132.51</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -1944,11 +1944,11 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215284035 ORD. MINISTERO PUBBLICA ISTRUZIONE STIPENDIO</t>
+          <t>ACCREDITO STIPENDIO MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>2116.08</v>
+        <v>2096.21</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -1958,15 +1958,15 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ENEL SERVIZIO ELETTRICO NAZ.</t>
+          <t>GIROCONTO DA CC 0123456 A CC 0468012 ACCANTONAMENTO RISPARMIO</t>
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>-144.95</v>
+        <v>-518.35</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Saldo finale: 13.201,49 EUR</t>
+          <t>Saldo finale: 19.239,75 EUR</t>
         </is>
       </c>
     </row>
